--- a/Top500_Crypto_latest.xlsx
+++ b/Top500_Crypto_latest.xlsx
@@ -66230,36 +66230,28 @@
         <v>5.09254</v>
       </c>
       <c r="J501" t="n">
-        <v>0.03758983944895399</v>
-      </c>
-      <c r="K501" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L501" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M501" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.03548</v>
+      </c>
+      <c r="K501" s="4" t="n">
+        <v>-10.40404040404042</v>
+      </c>
+      <c r="L501" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="M501" s="4" t="n">
+        <v>21.19503945885005</v>
       </c>
       <c r="N501" t="n">
-        <v>0.04506644863342069</v>
-      </c>
-      <c r="O501" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0439</v>
+      </c>
+      <c r="O501" s="4" t="n">
+        <v>2.093023255813965</v>
       </c>
       <c r="P501" t="n">
         <v>0.04919</v>
       </c>
       <c r="Q501" s="4" t="n">
-        <v>9.149936353141731</v>
+        <v>12.05011389521639</v>
       </c>
       <c r="R501" t="n">
         <v>0.05005</v>
@@ -66319,24 +66311,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AJ501" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AJ501" s="2" t="n">
+        <v>0.1666</v>
       </c>
       <c r="AK501" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AL501" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AL501" s="4" t="n">
+        <v>-73.56549819927972</v>
       </c>
       <c r="AM501" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>first-listing</t>
         </is>
       </c>
     </row>
@@ -66499,7 +66487,7 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11T08:42:44+00:00</t>
+          <t>2026-10-11T08:44:40+00:00</t>
         </is>
       </c>
     </row>
